--- a/data/glendaDatabase.xlsx
+++ b/data/glendaDatabase.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jonat\Documents\project\agenda\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5091E52F-6C49-438B-9D5A-9B9B72704D15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D09CF16-3234-45D0-9550-EBB4AE74FB90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{03EB8269-13C9-4F10-ADAF-64E5165EE7D6}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Glenducha" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Glenducha!$B$1:$I$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Glenducha!$D$1:$K$3</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="21">
   <si>
     <t>Fecha de Inicio</t>
   </si>
@@ -88,6 +88,18 @@
   </si>
   <si>
     <t>Dra. A</t>
+  </si>
+  <si>
+    <t>Historia Clinica</t>
+  </si>
+  <si>
+    <t>Numero Pieza Dental</t>
+  </si>
+  <si>
+    <t>Anterior</t>
+  </si>
+  <si>
+    <t>Retratamiento</t>
   </si>
 </sst>
 </file>
@@ -117,10 +129,11 @@
     </font>
     <font>
       <u/>
-      <sz val="8"/>
+      <sz val="11"/>
       <color theme="1"/>
-      <name val="Tahoma"/>
+      <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -172,9 +185,7 @@
     <xf numFmtId="2" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -489,107 +500,132 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C023E811-B4A1-4AE6-BF04-6A1C80397389}">
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:K4"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="13" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.85546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="18.85546875" customWidth="1"/>
-    <col min="9" max="9" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13" customWidth="1"/>
+    <col min="3" max="3" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.85546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="18.85546875" customWidth="1"/>
+    <col min="11" max="11" width="9.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>14</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="5" t="s">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B2" s="2">
+      <c r="B2" s="3">
+        <v>1234</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2" s="2">
         <v>44944</v>
       </c>
-      <c r="C2" s="2">
+      <c r="E2" s="2">
         <v>44951</v>
       </c>
-      <c r="D2" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E2" s="3">
+      <c r="F2" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G2" s="3">
         <v>23</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="H2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="I2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H2" s="3" t="s">
+      <c r="J2" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="I2" s="4">
+      <c r="K2" s="4">
         <v>50</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B3" s="2">
+      <c r="B3" s="3">
+        <v>5678</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3" s="2">
         <v>44951</v>
       </c>
-      <c r="C3" s="2">
+      <c r="E3" s="2">
         <v>44972</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="F3" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G3" s="3">
         <v>5</v>
       </c>
-      <c r="E3" s="3">
-        <v>5</v>
-      </c>
-      <c r="F3" s="3" t="s">
+      <c r="H3" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="I3" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="J3" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="I3" s="4">
+      <c r="K3" s="4">
         <v>120</v>
       </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="F4" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>